--- a/artfynd/Kälkåsen artfynd.xlsx
+++ b/artfynd/Kälkåsen artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55683415</v>
+        <v>55683418</v>
       </c>
       <c r="B2" t="n">
-        <v>91406</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687456</v>
+        <v>687523</v>
       </c>
       <c r="R2" t="n">
-        <v>7091907</v>
+        <v>7091759</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -797,52 +797,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96972204</v>
+        <v>55683419</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnberget, Kälkåsen, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687980</v>
+        <v>687587</v>
       </c>
       <c r="R3" t="n">
-        <v>7092127</v>
+        <v>7091703</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,12 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,74 +886,81 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96972062</v>
+        <v>55683415</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>björnberget, björntjärnen, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687617</v>
+        <v>687456</v>
       </c>
       <c r="R4" t="n">
-        <v>7092492</v>
+        <v>7091907</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +984,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,73 +1008,78 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55683414</v>
+        <v>55683417</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687385</v>
+        <v>687482</v>
       </c>
       <c r="R5" t="n">
-        <v>7092263</v>
+        <v>7091795</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,6 +1132,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1120,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55683404</v>
+        <v>96972144</v>
       </c>
       <c r="B6" t="n">
-        <v>91263</v>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,37 +1174,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnberget, Ång</t>
+          <t>Björnberget, Kälkåsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687401</v>
+        <v>687477</v>
       </c>
       <c r="R6" t="n">
-        <v>7092819</v>
+        <v>7091889</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,22 +1231,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,65 +1245,55 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55683401</v>
+        <v>55683416</v>
       </c>
       <c r="B7" t="n">
-        <v>80112</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687282</v>
+        <v>687437</v>
       </c>
       <c r="R7" t="n">
-        <v>7093130</v>
+        <v>7091851</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1364,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>55683416</v>
+        <v>96972045</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,37 +1401,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687437</v>
+        <v>687589</v>
       </c>
       <c r="R8" t="n">
-        <v>7091851</v>
+        <v>7092550</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,22 +1458,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,43 +1472,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96972081</v>
+        <v>96972071</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,21 +1506,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1520,14 +1529,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnberget, Ång</t>
+          <t>Björnberget, Björntjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687638</v>
+        <v>687588</v>
       </c>
       <c r="R9" t="n">
-        <v>7092388</v>
+        <v>7092435</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,48 +1600,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>55683423</v>
+        <v>96972139</v>
       </c>
       <c r="B10" t="n">
-        <v>80112</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnberget, Ång</t>
+          <t>Björnberget, Kälkåsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>687941</v>
+        <v>687681</v>
       </c>
       <c r="R10" t="n">
-        <v>7092248</v>
+        <v>7092453</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1656,22 +1668,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,65 +1682,55 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>55683417</v>
+        <v>55683410</v>
       </c>
       <c r="B11" t="n">
-        <v>91406</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687482</v>
+        <v>687587</v>
       </c>
       <c r="R11" t="n">
-        <v>7091795</v>
+        <v>7092434</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1807,17 +1799,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1835,48 +1827,51 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>55683410</v>
+        <v>96972081</v>
       </c>
       <c r="B12" t="n">
-        <v>91210</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>687587</v>
+        <v>687638</v>
       </c>
       <c r="R12" t="n">
-        <v>7092434</v>
+        <v>7092388</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,22 +1895,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,43 +1909,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>55683421</v>
+        <v>55683407</v>
       </c>
       <c r="B13" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687954</v>
+        <v>687602</v>
       </c>
       <c r="R13" t="n">
-        <v>7092179</v>
+        <v>7092435</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2079,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>55683407</v>
+        <v>55683408</v>
       </c>
       <c r="B14" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687602</v>
+        <v>687605</v>
       </c>
       <c r="R14" t="n">
-        <v>7092435</v>
+        <v>7092430</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2173,17 +2148,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2204,7 +2179,7 @@
         <v>55683409</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2323,32 +2298,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>55683405</v>
+        <v>55683411</v>
       </c>
       <c r="B16" t="n">
-        <v>91506</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2358,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687455</v>
+        <v>687543</v>
       </c>
       <c r="R16" t="n">
-        <v>7092854</v>
+        <v>7092448</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2417,17 +2392,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2445,32 +2420,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>55683403</v>
+        <v>55683413</v>
       </c>
       <c r="B17" t="n">
-        <v>92547</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2480,10 +2455,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687333</v>
+        <v>687539</v>
       </c>
       <c r="R17" t="n">
-        <v>7093046</v>
+        <v>7092440</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2536,6 +2511,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2552,32 +2542,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96972132</v>
+        <v>96972062</v>
       </c>
       <c r="B18" t="n">
-        <v>92547</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2586,14 +2576,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björnberget, Kälkåsen, Ång</t>
+          <t>björnberget, björntjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>687804</v>
+        <v>687617</v>
       </c>
       <c r="R18" t="n">
-        <v>7092268</v>
+        <v>7092492</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2657,10 +2647,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96972139</v>
+        <v>55683406</v>
       </c>
       <c r="B19" t="n">
-        <v>92535</v>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,40 +2658,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björnberget, Kälkåsen, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>687681</v>
+        <v>687548</v>
       </c>
       <c r="R19" t="n">
-        <v>7092453</v>
+        <v>7092678</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2725,12 +2712,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2739,33 +2736,43 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>55683424</v>
+        <v>55683414</v>
       </c>
       <c r="B20" t="n">
-        <v>82792</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2773,34 +2780,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>687911</v>
+        <v>687385</v>
       </c>
       <c r="R20" t="n">
-        <v>7092277</v>
+        <v>7092263</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2853,21 +2865,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2884,32 +2881,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>55683408</v>
+        <v>55683405</v>
       </c>
       <c r="B21" t="n">
-        <v>80083</v>
+        <v>92183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2919,10 +2916,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>687605</v>
+        <v>687455</v>
       </c>
       <c r="R21" t="n">
-        <v>7092430</v>
+        <v>7092854</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2978,17 +2975,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3006,10 +3003,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>55683400</v>
+        <v>55683403</v>
       </c>
       <c r="B22" t="n">
-        <v>80083</v>
+        <v>93209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3017,21 +3014,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3041,10 +3038,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687282</v>
+        <v>687333</v>
       </c>
       <c r="R22" t="n">
-        <v>7093130</v>
+        <v>7093046</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3097,21 +3094,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3128,32 +3110,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>55683422</v>
+        <v>55683400</v>
       </c>
       <c r="B23" t="n">
-        <v>80112</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3163,10 +3145,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687975</v>
+        <v>687282</v>
       </c>
       <c r="R23" t="n">
-        <v>7092147</v>
+        <v>7093130</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3250,32 +3232,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>55683418</v>
+        <v>55683401</v>
       </c>
       <c r="B24" t="n">
-        <v>78647</v>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3285,10 +3267,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687523</v>
+        <v>687282</v>
       </c>
       <c r="R24" t="n">
-        <v>7091759</v>
+        <v>7093130</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3344,17 +3326,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3372,10 +3354,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96972123</v>
+        <v>55683424</v>
       </c>
       <c r="B25" t="n">
-        <v>82792</v>
+        <v>83173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,22 +3383,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Björnberget, Kälkåsen, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
         <v>687911</v>
       </c>
       <c r="R25" t="n">
-        <v>7092300</v>
+        <v>7092277</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3440,12 +3419,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3454,71 +3443,84 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>55683420</v>
+        <v>96972123</v>
       </c>
       <c r="B26" t="n">
-        <v>80119</v>
+        <v>83173</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Björnberget, Ång</t>
+          <t>Björnberget, Kälkåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687954</v>
+        <v>687911</v>
       </c>
       <c r="R26" t="n">
-        <v>7092179</v>
+        <v>7092300</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3542,22 +3544,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3566,43 +3558,33 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96972144</v>
+        <v>96972132</v>
       </c>
       <c r="B27" t="n">
-        <v>79598</v>
+        <v>93209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,21 +3592,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3637,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687477</v>
+        <v>687804</v>
       </c>
       <c r="R27" t="n">
-        <v>7091889</v>
+        <v>7092268</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3704,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96972045</v>
+        <v>55683421</v>
       </c>
       <c r="B28" t="n">
-        <v>82792</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,40 +3697,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687589</v>
+        <v>687954</v>
       </c>
       <c r="R28" t="n">
-        <v>7092550</v>
+        <v>7092179</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3772,12 +3751,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3786,33 +3775,43 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>55683419</v>
+        <v>96972211</v>
       </c>
       <c r="B29" t="n">
-        <v>78647</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,37 +3819,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Björnberget, Ång</t>
+          <t>Björnberget, Kälkåsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687587</v>
+        <v>687956</v>
       </c>
       <c r="R29" t="n">
-        <v>7091703</v>
+        <v>7092176</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3874,22 +3876,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3898,43 +3890,33 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>55683406</v>
+        <v>55683422</v>
       </c>
       <c r="B30" t="n">
-        <v>80112</v>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3966,10 +3948,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687548</v>
+        <v>687975</v>
       </c>
       <c r="R30" t="n">
-        <v>7092678</v>
+        <v>7092147</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4053,51 +4035,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96972071</v>
+        <v>55683423</v>
       </c>
       <c r="B31" t="n">
-        <v>82792</v>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Björnberget, Björntjärnen, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687588</v>
+        <v>687941</v>
       </c>
       <c r="R31" t="n">
-        <v>7092435</v>
+        <v>7092248</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4121,12 +4100,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4135,74 +4124,81 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>96972211</v>
+        <v>55683420</v>
       </c>
       <c r="B32" t="n">
-        <v>80083</v>
+        <v>80468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Björnberget, Kälkåsen, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687956</v>
+        <v>687954</v>
       </c>
       <c r="R32" t="n">
-        <v>7092176</v>
+        <v>7092179</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4226,12 +4222,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4240,71 +4246,85 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>55683413</v>
+        <v>96972204</v>
       </c>
       <c r="B33" t="n">
-        <v>80083</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Björnberget, Ång</t>
+          <t>Björnberget, Kälkåsen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687539</v>
+        <v>687980</v>
       </c>
       <c r="R33" t="n">
-        <v>7092440</v>
+        <v>7092127</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4328,22 +4348,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4352,158 +4362,26 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>55683411</v>
-      </c>
-      <c r="B34" t="n">
-        <v>80083</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Björnberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>687543</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7092448</v>
-      </c>
-      <c r="S34" t="n">
-        <v>5</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2015-06-05</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
